--- a/multi seed generators/merged 10 seeds/regression/results/aggregated/fidelity_mean_sd.xlsx
+++ b/multi seed generators/merged 10 seeds/regression/results/aggregated/fidelity_mean_sd.xlsx
@@ -1398,12 +1398,10 @@
       <c r="O18" s="2" t="n">
         <v>0.6350429577102925</v>
       </c>
-      <c r="P18" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P18" s="2"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.635043 ± 0</t>
+          <t xml:space="preserve">0.635043</t>
         </is>
       </c>
       <c r="R18" s="2" t="n">
@@ -1469,12 +1467,10 @@
       <c r="O19" t="n">
         <v>0.234001770082493</v>
       </c>
-      <c r="P19" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P19"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.234002 ± 0</t>
+          <t xml:space="preserve">0.234002</t>
         </is>
       </c>
       <c r="R19" t="n">
@@ -1540,12 +1536,10 @@
       <c r="O20" s="2" t="n">
         <v>0.7538892658400576</v>
       </c>
-      <c r="P20" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P20" s="2"/>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753889 ± 0</t>
+          <t xml:space="preserve">0.753889</t>
         </is>
       </c>
       <c r="R20" s="2" t="n">
@@ -1611,12 +1605,10 @@
       <c r="O21" t="n">
         <v>103.3663040262217</v>
       </c>
-      <c r="P21" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P21"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t xml:space="preserve">103.366 ± 0</t>
+          <t xml:space="preserve">103.366</t>
         </is>
       </c>
       <c r="R21" t="n">
@@ -3670,12 +3662,10 @@
       <c r="O50" s="2" t="n">
         <v>0.770665587918015</v>
       </c>
-      <c r="P50" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P50" s="2"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.770666 ± 0</t>
+          <t xml:space="preserve">0.770666</t>
         </is>
       </c>
       <c r="R50" s="2" t="n">
@@ -3741,12 +3731,10 @@
       <c r="O51" t="n">
         <v>0.029608017208390965</v>
       </c>
-      <c r="P51" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P51"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.029608 ± 0</t>
+          <t xml:space="preserve">0.029608</t>
         </is>
       </c>
       <c r="R51" t="n">
@@ -3812,12 +3800,10 @@
       <c r="O52" s="2" t="n">
         <v>0.8490976018837287</v>
       </c>
-      <c r="P52" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P52" s="2"/>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.849098 ± 0</t>
+          <t xml:space="preserve">0.849098</t>
         </is>
       </c>
       <c r="R52" s="2" t="n">
@@ -3883,12 +3869,10 @@
       <c r="O53" t="n">
         <v>12.50151179072276</v>
       </c>
-      <c r="P53" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P53"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t xml:space="preserve">12.5015 ± 0</t>
+          <t xml:space="preserve">12.5015</t>
         </is>
       </c>
       <c r="R53" t="n">
@@ -5942,12 +5926,10 @@
       <c r="O82" s="2" t="n">
         <v>0.7611771986970685</v>
       </c>
-      <c r="P82" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P82" s="2"/>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.761177 ± 0</t>
+          <t xml:space="preserve">0.761177</t>
         </is>
       </c>
       <c r="R82" s="2" t="n">
@@ -6013,12 +5995,10 @@
       <c r="O83" t="n">
         <v>0.05848175743670013</v>
       </c>
-      <c r="P83" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P83"/>
       <c r="Q83" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0584818 ± 0</t>
+          <t xml:space="preserve">0.0584818</t>
         </is>
       </c>
       <c r="R83" t="n">
@@ -6084,12 +6064,10 @@
       <c r="O84" s="2" t="n">
         <v>0.8001880437833089</v>
       </c>
-      <c r="P84" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P84" s="2"/>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.800188 ± 0</t>
+          <t xml:space="preserve">0.800188</t>
         </is>
       </c>
       <c r="R84" s="2" t="n">
@@ -6155,12 +6133,10 @@
       <c r="O85" t="n">
         <v>6.538456381107492</v>
       </c>
-      <c r="P85" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P85"/>
       <c r="Q85" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.53846 ± 0</t>
+          <t xml:space="preserve">6.53846</t>
         </is>
       </c>
       <c r="R85" t="n">
@@ -8214,12 +8190,10 @@
       <c r="O114" s="2" t="n">
         <v>0.52965</v>
       </c>
-      <c r="P114" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P114" s="2"/>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.52965 ± 0</t>
+          <t xml:space="preserve">0.52965</t>
         </is>
       </c>
       <c r="R114" s="2" t="n">
@@ -8285,12 +8259,10 @@
       <c r="O115" t="n">
         <v>0.42421363720633687</v>
       </c>
-      <c r="P115" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P115"/>
       <c r="Q115" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.424214 ± 0</t>
+          <t xml:space="preserve">0.424214</t>
         </is>
       </c>
       <c r="R115" t="n">
@@ -8356,12 +8328,10 @@
       <c r="O116" s="2" t="n">
         <v>0.5787031249999999</v>
       </c>
-      <c r="P116" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P116" s="2"/>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.578703 ± 0</t>
+          <t xml:space="preserve">0.578703</t>
         </is>
       </c>
       <c r="R116" s="2" t="n">
@@ -8427,12 +8397,10 @@
       <c r="O117" t="n">
         <v>61.45270668942703</v>
       </c>
-      <c r="P117" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P117"/>
       <c r="Q117" t="inlineStr">
         <is>
-          <t xml:space="preserve">61.4527 ± 0</t>
+          <t xml:space="preserve">61.4527</t>
         </is>
       </c>
       <c r="R117" t="n">
@@ -10486,12 +10454,10 @@
       <c r="O146" s="2" t="n">
         <v>0.9131975735479007</v>
       </c>
-      <c r="P146" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P146" s="2"/>
       <c r="Q146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.913198 ± 0</t>
+          <t xml:space="preserve">0.913198</t>
         </is>
       </c>
       <c r="R146" s="2" t="n">
@@ -10557,12 +10523,10 @@
       <c r="O147" t="n">
         <v>0.015391049898669459</v>
       </c>
-      <c r="P147" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P147"/>
       <c r="Q147" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.015391 ± 0</t>
+          <t xml:space="preserve">0.015391</t>
         </is>
       </c>
       <c r="R147" t="n">
@@ -10628,12 +10592,10 @@
       <c r="O148" s="2" t="n">
         <v>0.6985660618611964</v>
       </c>
-      <c r="P148" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P148" s="2"/>
       <c r="Q148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.698566 ± 0</t>
+          <t xml:space="preserve">0.698566</t>
         </is>
       </c>
       <c r="R148" s="2" t="n">
@@ -10699,12 +10661,10 @@
       <c r="O149" t="n">
         <v>1.1067540440868329</v>
       </c>
-      <c r="P149" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P149"/>
       <c r="Q149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.10675 ± 0</t>
+          <t xml:space="preserve">1.10675</t>
         </is>
       </c>
       <c r="R149" t="n">
@@ -11977,12 +11937,10 @@
       <c r="O167" t="n">
         <v>0.2911469351633472</v>
       </c>
-      <c r="P167" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P167"/>
       <c r="Q167" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.291147 ± 0</t>
+          <t xml:space="preserve">0.291147</t>
         </is>
       </c>
       <c r="R167" t="n">
@@ -12261,12 +12219,10 @@
       <c r="O171" t="n">
         <v>0.2911469351633472</v>
       </c>
-      <c r="P171" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P171"/>
       <c r="Q171" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.291147 ± 0</t>
+          <t xml:space="preserve">0.291147</t>
         </is>
       </c>
       <c r="R171" t="n">
@@ -12758,12 +12714,10 @@
       <c r="O178" s="2" t="n">
         <v>0.619444612286002</v>
       </c>
-      <c r="P178" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P178" s="2"/>
       <c r="Q178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.619445 ± 0</t>
+          <t xml:space="preserve">0.619445</t>
         </is>
       </c>
       <c r="R178" s="2" t="n">
@@ -12829,12 +12783,10 @@
       <c r="O179" t="n">
         <v>0.2911469351633472</v>
       </c>
-      <c r="P179" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P179"/>
       <c r="Q179" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.291147 ± 0</t>
+          <t xml:space="preserve">0.291147</t>
         </is>
       </c>
       <c r="R179" t="n">
@@ -12900,12 +12852,10 @@
       <c r="O180" s="2" t="n">
         <v>0.8655543323682668</v>
       </c>
-      <c r="P180" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P180" s="2"/>
       <c r="Q180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.865554 ± 0</t>
+          <t xml:space="preserve">0.865554</t>
         </is>
       </c>
       <c r="R180" s="2" t="n">
@@ -12971,12 +12921,10 @@
       <c r="O181" t="n">
         <v>64.00031021804406</v>
       </c>
-      <c r="P181" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P181"/>
       <c r="Q181" t="inlineStr">
         <is>
-          <t xml:space="preserve">64.0003 ± 0</t>
+          <t xml:space="preserve">64.0003</t>
         </is>
       </c>
       <c r="R181" t="n">
@@ -13113,12 +13061,10 @@
       <c r="O183" t="n">
         <v>0.2911469351633472</v>
       </c>
-      <c r="P183" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P183"/>
       <c r="Q183" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.291147 ± 0</t>
+          <t xml:space="preserve">0.291147</t>
         </is>
       </c>
       <c r="R183" t="n">
